--- a/dashboard-data.xlsx
+++ b/dashboard-data.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="1" r:id="Rabe785373cbe4876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Periods" sheetId="2" r:id="Rcf7762ae7df445b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regions" sheetId="3" r:id="Rbd3b151768e54da1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="R5755dfcf364a4a79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarketTrend" sheetId="5" r:id="R6250550af9b4425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="1" r:id="Ra646bc79cc9242af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Periods" sheetId="2" r:id="R308ea15ae5154bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regions" sheetId="3" r:id="Rab4f072121be441f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="4" r:id="R124cb13746044462"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarketTrend" sheetId="5" r:id="R99306a9ee1984c92"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -265,7 +265,7 @@
     <x:col min="2" max="2" width="5.429999828338623" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.139999866485596" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.429999828338623" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19.860000610351562" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24.139999389648438" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="7.139999866485596" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="7.429999828338623" hidden="0" customWidth="1"/>
@@ -327,7 +327,7 @@
         <x:v>Q1</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>يناير 2026 - التقرير الأساسي</x:v>
+        <x:v>???? 2026 - ??????? ???????</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
         <x:v>March 2026 - Core Report</x:v>
@@ -365,7 +365,7 @@
         <x:v>Q2</x:v>
       </x:c>
       <x:c r="E3" s="7" t="str">
-        <x:v>أبريل 2026 - الربع الثاني</x:v>
+        <x:v>????? 2026 - ????? ??????</x:v>
       </x:c>
       <x:c r="F3" s="7" t="str">
         <x:v>June 2026 - Q2</x:v>
@@ -403,7 +403,7 @@
         <x:v>Q3</x:v>
       </x:c>
       <x:c r="E4" s="7" t="str">
-        <x:v>يوليو 2026 - الربع الثالث</x:v>
+        <x:v>?????? 2026 - ????? ??????</x:v>
       </x:c>
       <x:c r="F4" s="7" t="str">
         <x:v>September 2026 - Q3</x:v>
@@ -441,7 +441,7 @@
         <x:v>Q4</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
-        <x:v>أكتوبر 2026 - الربع الرابع</x:v>
+        <x:v>?????? 2026 - ????? ??????</x:v>
       </x:c>
       <x:c r="F5" s="7" t="str">
         <x:v>December 2026 - Q4</x:v>
@@ -479,7 +479,7 @@
         <x:v>Q1</x:v>
       </x:c>
       <x:c r="E6" s="7" t="str">
-        <x:v>يناير 2027 - الربع الأول</x:v>
+        <x:v>???? 2027 - ????? ?????</x:v>
       </x:c>
       <x:c r="F6" s="7" t="str">
         <x:v>March 2027 - Q1</x:v>
@@ -517,7 +517,7 @@
         <x:v>Q2</x:v>
       </x:c>
       <x:c r="E7" s="7" t="str">
-        <x:v>أبريل 2027 - الربع الثاني</x:v>
+        <x:v>????? 2027 - ????? ??????</x:v>
       </x:c>
       <x:c r="F7" s="7" t="str">
         <x:v>June 2027 - Q2</x:v>
@@ -555,7 +555,7 @@
         <x:v>Q3</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>يوليو 2027 - الربع الثالث</x:v>
+        <x:v>?????? 2027 - ????? ??????</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
         <x:v>September 2027 - Q3</x:v>
@@ -593,7 +593,7 @@
         <x:v>Q4</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>أكتوبر 2027 - الربع الرابع</x:v>
+        <x:v>?????? 2027 - ????? ??????</x:v>
       </x:c>
       <x:c r="F9" s="7" t="str">
         <x:v>December 2027 - Q4</x:v>
@@ -631,7 +631,7 @@
         <x:v>Q1</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>يناير 2028 - الربع الأول</x:v>
+        <x:v>???? 2028 - ????? ?????</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
         <x:v>March 2028 - Q1</x:v>
@@ -669,7 +669,7 @@
         <x:v>Q2</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>أبريل 2028 - الربع الثاني</x:v>
+        <x:v>????? 2028 - ????? ??????</x:v>
       </x:c>
       <x:c r="F11" s="7" t="str">
         <x:v>June 2028 - Q2</x:v>
@@ -707,7 +707,7 @@
         <x:v>Q3</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>يوليو 2028 - الربع الثالث</x:v>
+        <x:v>?????? 2028 - ????? ??????</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
         <x:v>September 2028 - Q3</x:v>
@@ -745,7 +745,7 @@
         <x:v>Q4</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
-        <x:v>أكتوبر 2028 - الربع الرابع</x:v>
+        <x:v>?????? 2028 - ????? ??????</x:v>
       </x:c>
       <x:c r="F13" s="7" t="str">
         <x:v>December 2028 - Q4</x:v>
@@ -783,7 +783,7 @@
         <x:v>Q1</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>يناير 2029 - الربع الأول</x:v>
+        <x:v>???? 2029 - ????? ?????</x:v>
       </x:c>
       <x:c r="F14" s="7" t="str">
         <x:v>March 2029 - Q1</x:v>
@@ -821,7 +821,7 @@
         <x:v>Q2</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>أبريل 2029 - الربع الثاني</x:v>
+        <x:v>????? 2029 - ????? ??????</x:v>
       </x:c>
       <x:c r="F15" s="7" t="str">
         <x:v>June 2029 - Q2</x:v>
@@ -859,7 +859,7 @@
         <x:v>Q3</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>يوليو 2029 - الربع الثالث</x:v>
+        <x:v>?????? 2029 - ????? ??????</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
         <x:v>September 2029 - Q3</x:v>
@@ -897,7 +897,7 @@
         <x:v>Q4</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>أكتوبر 2029 - الربع الرابع</x:v>
+        <x:v>?????? 2029 - ????? ??????</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
         <x:v>December 2029 - Q4</x:v>
@@ -935,7 +935,7 @@
         <x:v>Q1</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
-        <x:v>يناير 2030 - الربع الأول</x:v>
+        <x:v>???? 2030 - ????? ?????</x:v>
       </x:c>
       <x:c r="F18" s="7" t="str">
         <x:v>March 2030 - Q1</x:v>
@@ -973,7 +973,7 @@
         <x:v>Q2</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>أبريل 2030 - الربع الثاني</x:v>
+        <x:v>????? 2030 - ????? ??????</x:v>
       </x:c>
       <x:c r="F19" s="7" t="str">
         <x:v>June 2030 - Q2</x:v>
@@ -1011,7 +1011,7 @@
         <x:v>Q3</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
-        <x:v>يوليو 2030 - الربع الثالث</x:v>
+        <x:v>?????? 2030 - ????? ??????</x:v>
       </x:c>
       <x:c r="F20" s="7" t="str">
         <x:v>September 2030 - Q3</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>Q4</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>أكتوبر 2030 - الربع الرابع</x:v>
+        <x:v>?????? 2030 - ????? ??????</x:v>
       </x:c>
       <x:c r="F21" s="7" t="str">
         <x:v>December 2030 - Q4</x:v>
